--- a/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_15-06-2026.xlsx
+++ b/Compititor's_Price/Ecotherm_Prices/Ecotherm_Prices_15-06-2026.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Priyanka\Documents\Price_Comp_Dashboard\Compititor's_Price\Ecotherm_Prices\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{69D8F388-9198-4C3A-AE31-8F730262E8BC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5FD3FB5E-04E7-4832-B6CF-B4B461808719}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="32775" yWindow="1335" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="31860" yWindow="2325" windowWidth="21600" windowHeight="11550" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="187">
   <si>
     <t>Product</t>
   </si>
@@ -536,6 +536,51 @@
   </si>
   <si>
     <t>£95.89</t>
+  </si>
+  <si>
+    <t>SKU</t>
+  </si>
+  <si>
+    <t>ET25mm</t>
+  </si>
+  <si>
+    <t>ET30mm</t>
+  </si>
+  <si>
+    <t>ET40mm</t>
+  </si>
+  <si>
+    <t>ET50mm</t>
+  </si>
+  <si>
+    <t>ET60mm</t>
+  </si>
+  <si>
+    <t>ET70mm</t>
+  </si>
+  <si>
+    <t>ET75mm</t>
+  </si>
+  <si>
+    <t>ET80mm</t>
+  </si>
+  <si>
+    <t>ET90mm</t>
+  </si>
+  <si>
+    <t>ET100mm</t>
+  </si>
+  <si>
+    <t>ET110mm</t>
+  </si>
+  <si>
+    <t>ET120mm</t>
+  </si>
+  <si>
+    <t>ET130mm</t>
+  </si>
+  <si>
+    <t>ET140mm</t>
   </si>
 </sst>
 </file>
@@ -902,8 +947,8 @@
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
     <row r="1" spans="1:16" x14ac:dyDescent="0.25">
-      <c r="A1" t="s">
-        <v>143</v>
+      <c r="A1" s="1" t="s">
+        <v>172</v>
       </c>
       <c r="B1" s="1" t="s">
         <v>0</v>
@@ -953,7 +998,7 @@
     </row>
     <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>32</v>
+        <v>173</v>
       </c>
       <c r="B2" t="s">
         <v>15</v>
@@ -1003,7 +1048,7 @@
     </row>
     <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>174</v>
       </c>
       <c r="B3" t="s">
         <v>26</v>
@@ -1053,7 +1098,7 @@
     </row>
     <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>145</v>
+        <v>175</v>
       </c>
       <c r="B4" t="s">
         <v>34</v>
@@ -1103,7 +1148,7 @@
     </row>
     <row r="5" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>146</v>
+        <v>176</v>
       </c>
       <c r="B5" t="s">
         <v>42</v>
@@ -1153,7 +1198,7 @@
     </row>
     <row r="6" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>147</v>
+        <v>177</v>
       </c>
       <c r="B6" t="s">
         <v>50</v>
@@ -1203,7 +1248,7 @@
     </row>
     <row r="7" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>148</v>
+        <v>178</v>
       </c>
       <c r="B7" t="s">
         <v>59</v>
@@ -1253,7 +1298,7 @@
     </row>
     <row r="8" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>149</v>
+        <v>179</v>
       </c>
       <c r="B8" t="s">
         <v>68</v>
@@ -1303,7 +1348,7 @@
     </row>
     <row r="9" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
-        <v>150</v>
+        <v>180</v>
       </c>
       <c r="B9" t="s">
         <v>75</v>
@@ -1353,7 +1398,7 @@
     </row>
     <row r="10" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
-        <v>151</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
         <v>84</v>
@@ -1403,7 +1448,7 @@
     </row>
     <row r="11" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
-        <v>152</v>
+        <v>182</v>
       </c>
       <c r="B11" t="s">
         <v>93</v>
@@ -1453,7 +1498,7 @@
     </row>
     <row r="12" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
-        <v>152</v>
+        <v>183</v>
       </c>
       <c r="B12" t="s">
         <v>102</v>
@@ -1503,7 +1548,7 @@
     </row>
     <row r="13" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
-        <v>153</v>
+        <v>184</v>
       </c>
       <c r="B13" t="s">
         <v>108</v>
@@ -1553,7 +1598,7 @@
     </row>
     <row r="14" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
-        <v>154</v>
+        <v>185</v>
       </c>
       <c r="B14" t="s">
         <v>117</v>
@@ -1603,7 +1648,7 @@
     </row>
     <row r="15" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
-        <v>155</v>
+        <v>186</v>
       </c>
       <c r="B15" t="s">
         <v>125</v>
